--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Big Excel for Deepta.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Big Excel for Deepta.xlsx
@@ -22028,16 +22028,16 @@
         <v>69</v>
       </c>
       <c r="F201">
-        <v>-25.34777625570777</v>
+        <v>-25.51283072916668</v>
       </c>
       <c r="G201">
-        <v>0.9839699474178645</v>
+        <v>0.9836660061469258</v>
       </c>
       <c r="H201">
-        <v>-40.44520090049954</v>
+        <v>-51.02492880430024</v>
       </c>
       <c r="I201">
-        <v>0.001469934715911836</v>
+        <v>0.0005979614556156365</v>
       </c>
       <c r="J201">
         <v>0</v>
@@ -22046,22 +22046,22 @@
         <v>0</v>
       </c>
       <c r="L201">
-        <v>2148.732275393787</v>
+        <v>2150.366522061056</v>
       </c>
       <c r="M201">
-        <v>-0.01324032289739546</v>
+        <v>-0.01331145795412829</v>
       </c>
       <c r="N201">
-        <v>0.9892115104866116</v>
+        <v>0.9890300653205052</v>
       </c>
       <c r="O201">
-        <v>3028.309350850581</v>
+        <v>3158.109289683746</v>
       </c>
       <c r="P201">
-        <v>-0.01499471720267954</v>
+        <v>-0.01883073467678826</v>
       </c>
       <c r="Q201">
-        <v>0.1684330362035024</v>
+        <v>0.3474948702382935</v>
       </c>
       <c r="R201">
         <v>0</v>
@@ -22076,10 +22076,10 @@
         <v>0</v>
       </c>
       <c r="V201">
-        <v>-0.01188852614636213</v>
+        <v>-0.01196593942330978</v>
       </c>
       <c r="W201">
-        <v>0.006554298459207288</v>
+        <v>-0.003427821772579619</v>
       </c>
       <c r="X201">
         <v>0</v>
@@ -22088,22 +22088,22 @@
         <v>0</v>
       </c>
       <c r="Z201">
-        <v>1.007790963669335</v>
+        <v>1.008557451787594</v>
       </c>
       <c r="AA201">
-        <v>-0.01324032300441529</v>
+        <v>-0.01331145798838147</v>
       </c>
       <c r="AB201">
-        <v>0.9892115104866116</v>
+        <v>0.9890300653205052</v>
       </c>
       <c r="AC201">
-        <v>1.250489955102047</v>
+        <v>1.149953237454785</v>
       </c>
       <c r="AD201">
-        <v>0.004659738626698712</v>
+        <v>-0.002894264085899072</v>
       </c>
       <c r="AE201">
-        <v>0.001359232461461413</v>
+        <v>0.0005667511682240223</v>
       </c>
       <c r="AF201">
         <v>0</v>
@@ -22135,16 +22135,16 @@
         <v>70</v>
       </c>
       <c r="F202">
-        <v>-15.79503993865031</v>
+        <v>-15.95252035906642</v>
       </c>
       <c r="G202">
-        <v>0.9629491184693555</v>
+        <v>0.959437910082201</v>
       </c>
       <c r="H202">
-        <v>-22.23090709242568</v>
+        <v>-23.78829999786189</v>
       </c>
       <c r="I202">
-        <v>0.3361073326227472</v>
+        <v>0.472005057952524</v>
       </c>
       <c r="J202">
         <v>0</v>
@@ -22153,22 +22153,22 @@
         <v>0</v>
       </c>
       <c r="L202">
-        <v>2042.248169427113</v>
+        <v>2045.696134012479</v>
       </c>
       <c r="M202">
-        <v>-0.008966093065965434</v>
+        <v>-0.009050311934860372</v>
       </c>
       <c r="N202">
-        <v>0.9705920221975501</v>
+        <v>0.9676669380081462</v>
       </c>
       <c r="O202">
-        <v>2746.065174494848</v>
+        <v>2797.748039646864</v>
       </c>
       <c r="P202">
-        <v>-0.009429406167838375</v>
+        <v>-0.01007201979791761</v>
       </c>
       <c r="Q202">
-        <v>0.3380329790557827</v>
+        <v>0.4784785194304837</v>
       </c>
       <c r="R202">
         <v>0</v>
@@ -22183,10 +22183,10 @@
         <v>0</v>
       </c>
       <c r="V202">
-        <v>-0.007415511708286531</v>
+        <v>-0.007489446177965458</v>
       </c>
       <c r="W202">
-        <v>-0.007860714507573354</v>
+        <v>-0.008411399234690286</v>
       </c>
       <c r="X202">
         <v>0</v>
@@ -22195,22 +22195,22 @@
         <v>0</v>
       </c>
       <c r="Z202">
-        <v>0.9588019722834153</v>
+        <v>0.9604207324742061</v>
       </c>
       <c r="AA202">
-        <v>-0.008966094120665041</v>
+        <v>-0.009050312815682171</v>
       </c>
       <c r="AB202">
-        <v>0.9705920221975639</v>
+        <v>0.9676669380081566</v>
       </c>
       <c r="AC202">
-        <v>0.9709921015134588</v>
+        <v>0.9892668026036268</v>
       </c>
       <c r="AD202">
-        <v>-0.009429408840489525</v>
+        <v>-0.01007201908692574</v>
       </c>
       <c r="AE202">
-        <v>0.338032979055828</v>
+        <v>0.478478519430479</v>
       </c>
       <c r="AF202">
         <v>0</v>
@@ -22242,94 +22242,94 @@
         <v>71</v>
       </c>
       <c r="F203">
-        <v>-40.54558234398782</v>
+        <v>-42.08225486111111</v>
       </c>
       <c r="G203">
-        <v>0.7687405537859245</v>
+        <v>0.7666158732515267</v>
       </c>
       <c r="H203">
-        <v>-25.41726111389919</v>
+        <v>-38.67217056018004</v>
       </c>
       <c r="I203">
-        <v>0.04273937468490618</v>
+        <v>0.1386467206168687</v>
       </c>
       <c r="J203">
-        <v>-15.19780608828004</v>
+        <v>-16.56942413194443</v>
       </c>
       <c r="K203">
-        <v>15.02793978660035</v>
+        <v>12.3527582441202</v>
       </c>
       <c r="L203">
-        <v>2435.436972786841</v>
+        <v>2454.220935963442</v>
       </c>
       <c r="M203">
-        <v>-0.02030415770058236</v>
+        <v>-0.02104001488466816</v>
       </c>
       <c r="N203">
-        <v>0.7926621721453889</v>
+        <v>0.7919417022836213</v>
       </c>
       <c r="O203">
-        <v>2938.893102381838</v>
+        <v>3122.576762067089</v>
       </c>
       <c r="P203">
-        <v>-0.009689870243861094</v>
+        <v>-0.01428866403252922</v>
       </c>
       <c r="Q203">
-        <v>0.04414760524961148</v>
+        <v>0.1421702049589109</v>
       </c>
       <c r="R203">
-        <v>286.7046973930537</v>
+        <v>303.8544139023857</v>
       </c>
       <c r="S203">
-        <v>-0.0070638348031869</v>
+        <v>-0.007728556930539865</v>
       </c>
       <c r="T203">
-        <v>-89.41624846874265</v>
+        <v>-35.53252761665635</v>
       </c>
       <c r="U203">
-        <v>0.005304846958818448</v>
+        <v>0.004542070644259032</v>
       </c>
       <c r="V203">
-        <v>-0.01538191805305075</v>
+        <v>-0.01596489083001645</v>
       </c>
       <c r="W203">
-        <v>-0.007346706067856137</v>
+        <v>-0.01117795772087645</v>
       </c>
       <c r="X203">
-        <v>-0.003493391906688625</v>
+        <v>-0.003998951406706669</v>
       </c>
       <c r="Y203">
-        <v>-0.01390100452706343</v>
+        <v>-0.007750135948296831</v>
       </c>
       <c r="Z203">
-        <v>0.923940515416268</v>
+        <v>0.931066284507141</v>
       </c>
       <c r="AA203">
-        <v>-0.02030420684417391</v>
+        <v>-0.02104001273397468</v>
       </c>
       <c r="AB203">
-        <v>0.7926621721461442</v>
+        <v>0.7919417022835978</v>
       </c>
       <c r="AC203">
-        <v>0.8494698282819207</v>
+        <v>0.9025624824956506</v>
       </c>
       <c r="AD203">
-        <v>-0.009689942172751122</v>
+        <v>-0.01428873399250245</v>
       </c>
       <c r="AE203">
-        <v>0.044147605251043</v>
+        <v>0.1421702049611955</v>
       </c>
       <c r="AF203">
-        <v>-0.08385044825306698</v>
+        <v>-0.07749116728045335</v>
       </c>
       <c r="AG203">
-        <v>-0.00706388383975862</v>
+        <v>-0.007728554745593206</v>
       </c>
       <c r="AH203">
-        <v>-0.4010201268201267</v>
+        <v>-0.2473907549591343</v>
       </c>
       <c r="AI203">
-        <v>-0.01434968079944983</v>
+        <v>-0.01139446990660338</v>
       </c>
     </row>
     <row r="204" spans="1:35">
@@ -22349,94 +22349,94 @@
         <v>72</v>
       </c>
       <c r="F204">
-        <v>-16.39489769938651</v>
+        <v>-16.53456750448833</v>
       </c>
       <c r="G204">
-        <v>0.9722456183843224</v>
+        <v>0.9695611958937589</v>
       </c>
       <c r="H204">
-        <v>-20.99913875789335</v>
+        <v>-22.917601125196</v>
       </c>
       <c r="I204">
-        <v>0.341539749014434</v>
+        <v>0.4886292103548308</v>
       </c>
       <c r="J204">
-        <v>-0.5998577607362012</v>
+        <v>-0.5820471454219067</v>
       </c>
       <c r="K204">
-        <v>1.23176833453233</v>
+        <v>0.8706988726658906</v>
       </c>
       <c r="L204">
-        <v>2043.771139815872</v>
+        <v>2046.789078279165</v>
       </c>
       <c r="M204">
-        <v>-0.009334866457932401</v>
+        <v>-0.009408630691028345</v>
       </c>
       <c r="N204">
-        <v>0.9781449493327519</v>
+        <v>0.9760084974767634</v>
       </c>
       <c r="O204">
-        <v>2716.824802110256</v>
+        <v>2769.469947682058</v>
       </c>
       <c r="P204">
-        <v>-0.008875067750646143</v>
+        <v>-0.00970183083476169</v>
       </c>
       <c r="Q204">
-        <v>0.341488733535636</v>
+        <v>0.492987074536529</v>
       </c>
       <c r="R204">
-        <v>1.522970388759177</v>
+        <v>1.092944266686345</v>
       </c>
       <c r="S204">
-        <v>-0.0003687733919669669</v>
+        <v>-0.0003583187561679736</v>
       </c>
       <c r="T204">
-        <v>-29.24037238459186</v>
+        <v>-28.2780919648053</v>
       </c>
       <c r="U204">
-        <v>0.0005543384171922319</v>
+        <v>0.0003701889631559149</v>
       </c>
       <c r="V204">
-        <v>-0.007748544663176771</v>
+        <v>-0.007814555305193108</v>
       </c>
       <c r="W204">
-        <v>-0.007481531283597486</v>
+        <v>-0.008165037230334666</v>
       </c>
       <c r="X204">
-        <v>-0.0003330329548902394</v>
+        <v>-0.0003251091272276499</v>
       </c>
       <c r="Y204">
-        <v>0.0003791832239758682</v>
+        <v>0.00024636200435562</v>
       </c>
       <c r="Z204">
-        <v>0.9659256372855829</v>
+        <v>0.9673519760997289</v>
       </c>
       <c r="AA204">
-        <v>-0.009334866673917072</v>
+        <v>-0.009408631119787469</v>
       </c>
       <c r="AB204">
-        <v>0.978144949332753</v>
+        <v>0.9760084974767653</v>
       </c>
       <c r="AC204">
-        <v>0.9679449196745802</v>
+        <v>0.9867012134246115</v>
       </c>
       <c r="AD204">
-        <v>-0.008875067517985596</v>
+        <v>-0.009701829632030081</v>
       </c>
       <c r="AE204">
-        <v>0.341488733535636</v>
+        <v>0.4929870745365205</v>
       </c>
       <c r="AF204">
-        <v>0.007123665002167545</v>
+        <v>0.006931243625522776</v>
       </c>
       <c r="AG204">
-        <v>-0.0003687725532520308</v>
+        <v>-0.0003583183041052981</v>
       </c>
       <c r="AH204">
-        <v>-0.003047181838878643</v>
+        <v>-0.002565589179015282</v>
       </c>
       <c r="AI204">
-        <v>0.0005543413225039297</v>
+        <v>0.0003701894548956627</v>
       </c>
     </row>
     <row r="205" spans="1:35">
@@ -22456,94 +22456,94 @@
         <v>73</v>
       </c>
       <c r="F205">
-        <v>-39.82358660578387</v>
+        <v>-41.65550034722224</v>
       </c>
       <c r="G205">
-        <v>0.6982983535782953</v>
+        <v>0.6984360571968571</v>
       </c>
       <c r="H205">
-        <v>-31.0318094263801</v>
+        <v>-44.66941711241777</v>
       </c>
       <c r="I205">
-        <v>0.05909715217862088</v>
+        <v>0.1694794122220918</v>
       </c>
       <c r="J205">
-        <v>-14.47581035007609</v>
+        <v>-16.14266961805555</v>
       </c>
       <c r="K205">
-        <v>9.41339147411944</v>
+        <v>6.355511691882469</v>
       </c>
       <c r="L205">
-        <v>2400.50737183101</v>
+        <v>2423.219373975626</v>
       </c>
       <c r="M205">
-        <v>-0.02031625457351553</v>
+        <v>-0.02121943341410928</v>
       </c>
       <c r="N205">
-        <v>0.7228669929472499</v>
+        <v>0.7247260923490841</v>
       </c>
       <c r="O205">
-        <v>2990.123774341192</v>
+        <v>3175.55750844978</v>
       </c>
       <c r="P205">
-        <v>-0.01167557856797476</v>
+        <v>-0.01630202529379313</v>
       </c>
       <c r="Q205">
-        <v>0.06029608477614368</v>
+        <v>0.1717385350930799</v>
       </c>
       <c r="R205">
-        <v>251.7750964372226</v>
+        <v>272.8528519145693</v>
       </c>
       <c r="S205">
-        <v>-0.007075931676120074</v>
+        <v>-0.007907975459980985</v>
       </c>
       <c r="T205">
-        <v>-38.18557650938919</v>
+        <v>17.44821876603419</v>
       </c>
       <c r="U205">
-        <v>0.003319138634704786</v>
+        <v>0.002528709382995122</v>
       </c>
       <c r="V205">
-        <v>-0.01498317520864651</v>
+        <v>-0.01567241208795642</v>
       </c>
       <c r="W205">
-        <v>-0.008844269946720015</v>
+        <v>-0.01273107790385598</v>
       </c>
       <c r="X205">
-        <v>-0.003094649062284382</v>
+        <v>-0.003706472664646639</v>
       </c>
       <c r="Y205">
-        <v>-0.0153985684059273</v>
+        <v>-0.009303256131276361</v>
       </c>
       <c r="Z205">
-        <v>0.9031643109716281</v>
+        <v>0.9117089239217001</v>
       </c>
       <c r="AA205">
-        <v>-0.0203163247641459</v>
+        <v>-0.02121942924346083</v>
       </c>
       <c r="AB205">
-        <v>0.7228669929469289</v>
+        <v>0.7247260923490132</v>
       </c>
       <c r="AC205">
-        <v>0.8522052157123022</v>
+        <v>0.905054544327157</v>
       </c>
       <c r="AD205">
-        <v>-0.01167561603815832</v>
+        <v>-0.01630199023912181</v>
       </c>
       <c r="AE205">
-        <v>0.06029608477690995</v>
+        <v>0.1717385350912644</v>
       </c>
       <c r="AF205">
-        <v>-0.1046266526977069</v>
+        <v>-0.09684852786589426</v>
       </c>
       <c r="AG205">
-        <v>-0.00707600175973061</v>
+        <v>-0.007907971255079355</v>
       </c>
       <c r="AH205">
-        <v>-0.3982847393897452</v>
+        <v>-0.2448986931276279</v>
       </c>
       <c r="AI205">
-        <v>-0.01633535466485703</v>
+        <v>-0.01340772615322274</v>
       </c>
     </row>
     <row r="206" spans="1:35">
@@ -22563,94 +22563,94 @@
         <v>74</v>
       </c>
       <c r="F206">
-        <v>-14.83990346625767</v>
+        <v>-15.00933017953321</v>
       </c>
       <c r="G206">
-        <v>0.9492113813256556</v>
+        <v>0.9449937517824649</v>
       </c>
       <c r="H206">
-        <v>-20.06953000976457</v>
+        <v>-22.67143176911338</v>
       </c>
       <c r="I206">
-        <v>0.3372647323706471</v>
+        <v>0.4922932791008753</v>
       </c>
       <c r="J206">
-        <v>0.9551364723926348</v>
+        <v>0.9431901795332145</v>
       </c>
       <c r="K206">
-        <v>2.161377082661108</v>
+        <v>1.116868228748512</v>
       </c>
       <c r="L206">
-        <v>2013.04176342722</v>
+        <v>2016.780500568934</v>
       </c>
       <c r="M206">
-        <v>-0.008503033375175786</v>
+        <v>-0.008595512013101596</v>
       </c>
       <c r="N206">
-        <v>0.9586770704002817</v>
+        <v>0.9550558927065033</v>
       </c>
       <c r="O206">
-        <v>2737.33011475925</v>
+        <v>2794.521029695591</v>
       </c>
       <c r="P206">
-        <v>-0.008433886987630132</v>
+        <v>-0.009565496842379183</v>
       </c>
       <c r="Q206">
-        <v>0.3401093396061412</v>
+        <v>0.5005379602765846</v>
       </c>
       <c r="R206">
-        <v>-29.2064059998927</v>
+        <v>-28.91563344354518</v>
       </c>
       <c r="S206">
-        <v>0.0004630596907896477</v>
+        <v>0.0004547999217587757</v>
       </c>
       <c r="T206">
-        <v>-8.735059735598043</v>
+        <v>-3.227009951272976</v>
       </c>
       <c r="U206">
-        <v>0.0009955191802082427</v>
+        <v>0.0005065229555384215</v>
       </c>
       <c r="V206">
-        <v>-0.007024114769413315</v>
+        <v>-0.007104308867828968</v>
       </c>
       <c r="W206">
-        <v>-0.007109093710934623</v>
+        <v>-0.008030747751904035</v>
       </c>
       <c r="X206">
-        <v>0.0003913969388732166</v>
+        <v>0.0003851373101364901</v>
       </c>
       <c r="Y206">
-        <v>0.0007516207966387313</v>
+        <v>0.0003806514827862512</v>
       </c>
       <c r="Z206">
-        <v>0.952825374263501</v>
+        <v>0.9545950186577422</v>
       </c>
       <c r="AA206">
-        <v>-0.008503034298885907</v>
+        <v>-0.008595513104292699</v>
       </c>
       <c r="AB206">
-        <v>0.9586770704002936</v>
+        <v>0.9550558927065183</v>
       </c>
       <c r="AC206">
-        <v>0.9696259563173422</v>
+        <v>0.9898844659795114</v>
       </c>
       <c r="AD206">
-        <v>-0.008433890227833526</v>
+        <v>-0.00956551118602161</v>
       </c>
       <c r="AE206">
-        <v>0.3401093396061903</v>
+        <v>0.5005379602778099</v>
       </c>
       <c r="AF206">
-        <v>-0.005976598019914348</v>
+        <v>-0.005825713816463907</v>
       </c>
       <c r="AG206">
-        <v>0.0004630598217791344</v>
+        <v>0.0004547997113894722</v>
       </c>
       <c r="AH206">
-        <v>-0.001366145196116664</v>
+        <v>0.0006176633758846473</v>
       </c>
       <c r="AI206">
-        <v>0.0009955186126559996</v>
+        <v>0.0005065079009041341</v>
       </c>
     </row>
     <row r="207" spans="1:35">
@@ -22670,94 +22670,94 @@
         <v>75</v>
       </c>
       <c r="F207">
-        <v>-37.24809589041097</v>
+        <v>-38.95669531250002</v>
       </c>
       <c r="G207">
-        <v>0.6990473556525569</v>
+        <v>0.6991849703213233</v>
       </c>
       <c r="H207">
-        <v>-15.98119477879285</v>
+        <v>-38.33408616303024</v>
       </c>
       <c r="I207">
-        <v>0.01201373147481311</v>
+        <v>0.09839634029505462</v>
       </c>
       <c r="J207">
-        <v>-11.90031963470319</v>
+        <v>-13.44386458333333</v>
       </c>
       <c r="K207">
-        <v>24.4640061217067</v>
+        <v>12.69084264127</v>
       </c>
       <c r="L207">
-        <v>2326.22894186463</v>
+        <v>2347.306182954766</v>
       </c>
       <c r="M207">
-        <v>-0.01943484551196308</v>
+        <v>-0.0202977309054456</v>
       </c>
       <c r="N207">
-        <v>0.7223640805923343</v>
+        <v>0.7241568640327998</v>
       </c>
       <c r="O207">
-        <v>2787.142979795157</v>
+        <v>3078.570075475997</v>
       </c>
       <c r="P207">
-        <v>-0.006087023650921537</v>
+        <v>-0.01412339024012586</v>
       </c>
       <c r="Q207">
-        <v>0.01211625300041197</v>
+        <v>0.09932112188205655</v>
       </c>
       <c r="R207">
-        <v>177.4966664708427</v>
+        <v>196.9396608937095</v>
       </c>
       <c r="S207">
-        <v>-0.00619452261456762</v>
+        <v>-0.006986272951317308</v>
       </c>
       <c r="T207">
-        <v>-241.166371055424</v>
+        <v>-79.53921420774896</v>
       </c>
       <c r="U207">
-        <v>0.008907693551758005</v>
+        <v>0.004707344436662398</v>
       </c>
       <c r="V207">
-        <v>-0.01450707724134544</v>
+        <v>-0.01517252827174684</v>
       </c>
       <c r="W207">
-        <v>-0.004662427101515779</v>
+        <v>-0.01118376221004006</v>
       </c>
       <c r="X207">
-        <v>-0.00261855109498331</v>
+        <v>-0.003206588848437055</v>
       </c>
       <c r="Y207">
-        <v>-0.01121672556072307</v>
+        <v>-0.007755940437460441</v>
       </c>
       <c r="Z207">
-        <v>0.9060005890366406</v>
+        <v>0.914209518873379</v>
       </c>
       <c r="AA207">
-        <v>-0.01943489820619822</v>
+        <v>-0.02029777582119136</v>
       </c>
       <c r="AB207">
-        <v>0.7223640805914968</v>
+        <v>0.7241568640372702</v>
       </c>
       <c r="AC207">
-        <v>0.813133881962144</v>
+        <v>0.8981562172322497</v>
       </c>
       <c r="AD207">
-        <v>-0.006087023492901915</v>
+        <v>-0.01412339813763866</v>
       </c>
       <c r="AE207">
-        <v>0.01211625300041164</v>
+        <v>0.09932112188209119</v>
       </c>
       <c r="AF207">
-        <v>-0.1017903746326944</v>
+        <v>-0.09434793291421539</v>
       </c>
       <c r="AG207">
-        <v>-0.006194575201782928</v>
+        <v>-0.006986317832809888</v>
       </c>
       <c r="AH207">
-        <v>-0.4373560731399034</v>
+        <v>-0.2517970202225353</v>
       </c>
       <c r="AI207">
-        <v>-0.01074676211960063</v>
+        <v>-0.01122913405173959</v>
       </c>
     </row>
     <row r="208" spans="1:35">
@@ -22777,94 +22777,94 @@
         <v>76</v>
       </c>
       <c r="F208">
-        <v>-14.47265358895706</v>
+        <v>-14.65670070017953</v>
       </c>
       <c r="G208">
-        <v>0.9383255243828198</v>
+        <v>0.9333542304502315</v>
       </c>
       <c r="H208">
-        <v>-18.71683761046534</v>
+        <v>-21.38853655057304</v>
       </c>
       <c r="I208">
-        <v>0.3141189155506438</v>
+        <v>0.474200795796484</v>
       </c>
       <c r="J208">
-        <v>1.322386349693247</v>
+        <v>1.295819658886893</v>
       </c>
       <c r="K208">
-        <v>3.514069481960334</v>
+        <v>2.399763447288851</v>
       </c>
       <c r="L208">
-        <v>2001.660855881178</v>
+        <v>2005.752176940943</v>
       </c>
       <c r="M208">
-        <v>-0.008319931308255115</v>
+        <v>-0.008421620814611258</v>
       </c>
       <c r="N208">
-        <v>0.9480704254329484</v>
+        <v>0.9437482519697301</v>
       </c>
       <c r="O208">
-        <v>2693.482882176217</v>
+        <v>2751.27815841052</v>
       </c>
       <c r="P208">
-        <v>-0.0079006214424161</v>
+        <v>-0.009067805195459102</v>
       </c>
       <c r="Q208">
-        <v>0.3156560235117959</v>
+        <v>0.4805821769122466</v>
       </c>
       <c r="R208">
-        <v>-40.58731354593465</v>
+        <v>-39.94395707153581</v>
       </c>
       <c r="S208">
-        <v>0.0006461617577103191</v>
+        <v>0.0006286911202491134</v>
       </c>
       <c r="T208">
-        <v>-52.58229231863061</v>
+        <v>-46.46988123634401</v>
       </c>
       <c r="U208">
-        <v>0.001528784725422274</v>
+        <v>0.001004214602458503</v>
       </c>
       <c r="V208">
-        <v>-0.006846183344240307</v>
+        <v>-0.006933245489386119</v>
       </c>
       <c r="W208">
-        <v>-0.006664896602045742</v>
+        <v>-0.007616264432349328</v>
       </c>
       <c r="X208">
-        <v>0.0005693283640462246</v>
+        <v>0.0005562006885793391</v>
       </c>
       <c r="Y208">
-        <v>0.001195817905527612</v>
+        <v>0.0007951348023409587</v>
       </c>
       <c r="Z208">
-        <v>0.9468710947026343</v>
+        <v>0.9488064665287333</v>
       </c>
       <c r="AA208">
-        <v>-0.008319931976041939</v>
+        <v>-0.008421621642166574</v>
       </c>
       <c r="AB208">
-        <v>0.9480704254329553</v>
+        <v>0.943748251969739</v>
       </c>
       <c r="AC208">
-        <v>0.9591248635386419</v>
+        <v>0.9797053966212678</v>
       </c>
       <c r="AD208">
-        <v>-0.007900619234677084</v>
+        <v>-0.009067814081801446</v>
       </c>
       <c r="AE208">
-        <v>0.3156560235117505</v>
+        <v>0.4805821769127258</v>
       </c>
       <c r="AF208">
-        <v>-0.01193087758078104</v>
+        <v>-0.01161426594547277</v>
       </c>
       <c r="AG208">
-        <v>0.0006461621446231022</v>
+        <v>0.0006286911735155967</v>
       </c>
       <c r="AH208">
-        <v>-0.01186723797481692</v>
+        <v>-0.009561405982358995</v>
       </c>
       <c r="AI208">
-        <v>0.001528789605812441</v>
+        <v>0.001004205005124298</v>
       </c>
     </row>
     <row r="209" spans="1:35">
@@ -22884,94 +22884,94 @@
         <v>77</v>
       </c>
       <c r="F209">
-        <v>-32.78490593607305</v>
+        <v>-34.19849583333333</v>
       </c>
       <c r="G209">
-        <v>0.7241542783143873</v>
+        <v>0.7232644068328073</v>
       </c>
       <c r="H209">
-        <v>-50.44940918901094</v>
+        <v>-67.07557218390926</v>
       </c>
       <c r="I209">
-        <v>0.2027972034858614</v>
+        <v>0.4043194761784185</v>
       </c>
       <c r="J209">
-        <v>-7.437129680365278</v>
+        <v>-8.685665104166649</v>
       </c>
       <c r="K209">
-        <v>-10.00420828851139</v>
+        <v>-16.05064337960902</v>
       </c>
       <c r="L209">
-        <v>1818.824351780833</v>
+        <v>1836.470795586583</v>
       </c>
       <c r="M209">
-        <v>-0.02249563958631041</v>
+        <v>-0.02342669772731555</v>
       </c>
       <c r="N209">
-        <v>0.75060606085834</v>
+        <v>0.7515055367236003</v>
       </c>
       <c r="O209">
-        <v>2717.156184160533</v>
+        <v>2925.154570876276</v>
       </c>
       <c r="P209">
-        <v>-0.02242772462568742</v>
+        <v>-0.02940584275725998</v>
       </c>
       <c r="Q209">
-        <v>0.2036369067768344</v>
+        <v>0.4087735818201634</v>
       </c>
       <c r="R209">
-        <v>-329.9079236129544</v>
+        <v>-313.8957264744738</v>
       </c>
       <c r="S209">
-        <v>-0.009255316688914956</v>
+        <v>-0.01011523977318726</v>
       </c>
       <c r="T209">
-        <v>-311.1531666900478</v>
+        <v>-232.9547188074703</v>
       </c>
       <c r="U209">
-        <v>-0.007433007423007879</v>
+        <v>-0.01057510808047173</v>
       </c>
       <c r="V209">
-        <v>-0.01630993286271761</v>
+        <v>-0.0170131697841438</v>
       </c>
       <c r="W209">
-        <v>-0.01736400478461703</v>
+        <v>-0.02308650537350642</v>
       </c>
       <c r="X209">
-        <v>-0.004421406716355483</v>
+        <v>-0.005047230360834019</v>
       </c>
       <c r="Y209">
-        <v>-0.02391830324382431</v>
+        <v>-0.0196586836009268</v>
       </c>
       <c r="Z209">
-        <v>0.904833841103619</v>
+        <v>0.9136123963699101</v>
       </c>
       <c r="AA209">
-        <v>-0.02249559273279371</v>
+        <v>-0.02342661412640402</v>
       </c>
       <c r="AB209">
-        <v>0.7506060608605669</v>
+        <v>0.7515055367257522</v>
       </c>
       <c r="AC209">
-        <v>0.9352084413540216</v>
+        <v>1.006798678952319</v>
       </c>
       <c r="AD209">
-        <v>-0.022427725582607</v>
+        <v>-0.0294058442716214</v>
       </c>
       <c r="AE209">
-        <v>0.2036369067768341</v>
+        <v>0.4087735818201665</v>
       </c>
       <c r="AF209">
-        <v>-0.102957122565716</v>
+        <v>-0.09494505541768428</v>
       </c>
       <c r="AG209">
-        <v>-0.009255269728378413</v>
+        <v>-0.01011515613802255</v>
       </c>
       <c r="AH209">
-        <v>-0.3152815137480258</v>
+        <v>-0.1431545585024661</v>
       </c>
       <c r="AI209">
-        <v>-0.02708746420930572</v>
+        <v>-0.02651158018572232</v>
       </c>
     </row>
     <row r="210" spans="1:35">
@@ -22991,94 +22991,94 @@
         <v>78</v>
       </c>
       <c r="F210">
-        <v>-13.69297058282208</v>
+        <v>-13.85916969479353</v>
       </c>
       <c r="G210">
-        <v>0.9449684190876556</v>
+        <v>0.9402471655704547</v>
       </c>
       <c r="H210">
-        <v>-19.19054423458723</v>
+        <v>-20.89774316990142</v>
       </c>
       <c r="I210">
-        <v>0.4183399339396588</v>
+        <v>0.5096866126368677</v>
       </c>
       <c r="J210">
-        <v>2.102069355828222</v>
+        <v>2.093350664272895</v>
       </c>
       <c r="K210">
-        <v>3.040362857838446</v>
+        <v>2.890556827960467</v>
       </c>
       <c r="L210">
-        <v>1957.842317927357</v>
+        <v>1961.520843833339</v>
       </c>
       <c r="M210">
-        <v>-0.007993733651853312</v>
+        <v>-0.008087019572132252</v>
       </c>
       <c r="N210">
-        <v>0.953111509834434</v>
+        <v>0.9490140083635862</v>
       </c>
       <c r="O210">
-        <v>2779.720124867089</v>
+        <v>2811.975148110661</v>
       </c>
       <c r="P210">
-        <v>-0.007631779060012486</v>
+        <v>-0.008288984198943637</v>
       </c>
       <c r="Q210">
-        <v>0.4104118523034009</v>
+        <v>0.4998294412504238</v>
       </c>
       <c r="R210">
-        <v>-84.4058514997555</v>
+        <v>-84.17529017914012</v>
       </c>
       <c r="S210">
-        <v>0.0009723594141121221</v>
+        <v>0.0009632923627281194</v>
       </c>
       <c r="T210">
-        <v>33.65495037224173</v>
+        <v>14.22710846379732</v>
       </c>
       <c r="U210">
-        <v>0.001797627107825888</v>
+        <v>0.001783035598973968</v>
       </c>
       <c r="V210">
-        <v>-0.006651587136718066</v>
+        <v>-0.00673232110665079</v>
       </c>
       <c r="W210">
-        <v>-0.006822112139142233</v>
+        <v>-0.007429010121719855</v>
       </c>
       <c r="X210">
-        <v>0.0007639245715684653</v>
+        <v>0.0007571250713146677</v>
       </c>
       <c r="Y210">
-        <v>0.001038602368431121</v>
+        <v>0.0009823891129704309</v>
       </c>
       <c r="Z210">
-        <v>0.9510543145397138</v>
+        <v>0.9528412192852667</v>
       </c>
       <c r="AA210">
-        <v>-0.007993733516736054</v>
+        <v>-0.008087019429023283</v>
       </c>
       <c r="AB210">
-        <v>0.9531115098344339</v>
+        <v>0.9490140083635861</v>
       </c>
       <c r="AC210">
-        <v>0.9881720516393807</v>
+        <v>0.9996386410447933</v>
       </c>
       <c r="AD210">
-        <v>-0.007631768610374409</v>
+        <v>-0.008288983382054523</v>
       </c>
       <c r="AE210">
-        <v>0.4104118523028164</v>
+        <v>0.4998294412504384</v>
       </c>
       <c r="AF210">
-        <v>-0.007747657743701564</v>
+        <v>-0.007579513188939457</v>
       </c>
       <c r="AG210">
-        <v>0.0009723606039289869</v>
+        <v>0.0009632933866588877</v>
       </c>
       <c r="AH210">
-        <v>0.01717995012592188</v>
+        <v>0.01037183844116651</v>
       </c>
       <c r="AI210">
-        <v>0.001797640230115117</v>
+        <v>0.001783035704871221</v>
       </c>
     </row>
     <row r="211" spans="1:35">
